--- a/artfynd/A 30069-2022 artfynd.xlsx
+++ b/artfynd/A 30069-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30069-2022 artfynd.xlsx
+++ b/artfynd/A 30069-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104036156</v>
+        <v>104036154</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473115.1733385284</v>
+        <v>473080</v>
       </c>
       <c r="R2" t="n">
-        <v>7011968.699309157</v>
+        <v>7011900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +772,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104036154</v>
+        <v>104036151</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Acksjön nv, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473080.2998850874</v>
+        <v>473028</v>
       </c>
       <c r="R3" t="n">
-        <v>7011900.475571569</v>
+        <v>7011824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +848,14 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,131 +879,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>104036151</v>
-      </c>
-      <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Acksjön nv, Jmt</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>473028.201883323</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7011823.830161586</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30069-2022 artfynd.xlsx
+++ b/artfynd/A 30069-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036154</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,8 +889,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104036151</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>